--- a/resources/item/item_recipe.xlsx
+++ b/resources/item/item_recipe.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="28680" yWindow="-1095" windowWidth="29040" windowHeight="15720" tabRatio="708" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="ItemRecipe" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="RecipeLevel" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="RecipeMaterial" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ItemRecipe" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RecipeLevel" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RecipeMaterial" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="181029" fullCalcOnLoad="1"/>
@@ -3722,7 +3722,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AL29"/>
+  <dimension ref="A1:AL30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16.75" customWidth="1" style="8" min="1" max="1"/>
@@ -7520,6 +7520,61 @@
       <c r="AK29" s="42" t="n"/>
       <c r="AL29" s="10" t="n"/>
     </row>
+    <row r="30">
+      <c r="A30" s="8" t="n">
+        <v>126</v>
+      </c>
+      <c r="C30" s="41" t="inlineStr">
+        <is>
+          <t>冰魄碎片</t>
+        </is>
+      </c>
+      <c r="D30" s="8" t="n"/>
+      <c r="E30" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="F30" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="G30" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="H30" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="I30" s="10" t="n">
+        <v>100</v>
+      </c>
+      <c r="J30" s="10" t="n"/>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="10" t="n"/>
+      <c r="M30" s="10" t="n"/>
+      <c r="N30" s="10" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="10" t="n"/>
+      <c r="R30" s="8" t="n"/>
+      <c r="S30" s="10" t="n"/>
+      <c r="T30" s="10" t="n"/>
+      <c r="U30" s="10" t="n"/>
+      <c r="V30" s="10" t="n"/>
+      <c r="W30" s="10" t="n"/>
+      <c r="X30" s="10" t="n"/>
+      <c r="Y30" s="8" t="n"/>
+      <c r="Z30" s="42" t="n"/>
+      <c r="AA30" s="42" t="n"/>
+      <c r="AB30" s="42" t="n"/>
+      <c r="AC30" s="42" t="n"/>
+      <c r="AD30" s="42" t="n"/>
+      <c r="AE30" s="10" t="n"/>
+      <c r="AF30" s="8" t="n"/>
+      <c r="AG30" s="42" t="n"/>
+      <c r="AH30" s="42" t="n"/>
+      <c r="AI30" s="42" t="n"/>
+      <c r="AJ30" s="42" t="n"/>
+      <c r="AK30" s="42" t="n"/>
+      <c r="AL30" s="10" t="n"/>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="A1:A4 A35:A1048576">
     <cfRule type="duplicateValues" priority="1991" dxfId="0"/>
